--- a/Wochenplan/Wochenuebersicht_20260526.xlsx
+++ b/Wochenplan/Wochenuebersicht_20260526.xlsx
@@ -39,7 +39,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -78,11 +78,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
@@ -105,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -143,19 +138,16 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -924,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -965,7 +957,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>DIENSTAG</t>
+          <t>MITTWOCH</t>
         </is>
       </c>
     </row>
@@ -973,13 +965,15 @@
       <c r="A4" s="14" t="inlineStr"/>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>MUERBETEIG BACKEN</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr"/>
+          <t>Kaesekuchen</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>Alle Boeden: 36x 30x20 Schnitte, 20x Murbeteig rund, 60x Tartelette + 4x Murbeteig rund fuer naechsten Montag</t>
+          <t>Charge 5/10 → 1 frisch, 1 einfrieren</t>
         </is>
       </c>
     </row>
@@ -995,7 +989,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Charge 7/10 → 1 frisch, 1 einfrieren</t>
+          <t>Charge 6/10 → 1 frisch, 1 einfrieren</t>
         </is>
       </c>
     </row>
@@ -1003,15 +997,15 @@
       <c r="A6" s="14" t="inlineStr"/>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>Kaesekuchen</t>
+          <t>Bienenstich</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>Charge 8/10 → 1 frisch, 1 einfrieren</t>
+          <t>Charge 3/3 → 1 frisch, 5 einfrieren</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1021,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>Charge 4/7 → 1 frisch, 2 einfrieren</t>
+          <t>Charge 3/7 → 1 frisch, 2 einfrieren</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1029,7 @@
       <c r="A8" s="14" t="inlineStr"/>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Kaese-Rhabarber Schnitte</t>
+          <t>Donauwelle</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
@@ -1043,30 +1037,30 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>Charge 2/3 → 2 frisch, 4 einfrieren</t>
+          <t>Charge 3/3 → 1 frisch, 5 einfrieren</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>MITTWOCH</t>
+      <c r="A9" s="14" t="inlineStr"/>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Beeren Tartelette</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>60 Stueck → 8 frisch, 52 einfrieren</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="14" t="inlineStr"/>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Kaesekuchen</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>Charge 5/10 → 1 frisch, 1 einfrieren</t>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>DONNERSTAG</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1076,7 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>Charge 6/10 → 1 frisch, 1 einfrieren</t>
+          <t>Charge 3/10</t>
         </is>
       </c>
     </row>
@@ -1090,15 +1084,15 @@
       <c r="A12" s="14" t="inlineStr"/>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Bienenstich</t>
+          <t>Kaesekuchen</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Charge 3/3 → 1 frisch, 5 einfrieren</t>
+          <t>Charge 4/10</t>
         </is>
       </c>
     </row>
@@ -1106,15 +1100,15 @@
       <c r="A13" s="14" t="inlineStr"/>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Lauch-Speck Quiche</t>
+          <t>Bienenstich</t>
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Charge 3/7 → 1 frisch, 2 einfrieren</t>
+          <t>Charge 2/3 → 1 frisch, 5 einfrieren</t>
         </is>
       </c>
     </row>
@@ -1122,15 +1116,15 @@
       <c r="A14" s="14" t="inlineStr"/>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Donauwelle</t>
+          <t>Lauch-Speck Quiche</t>
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Charge 3/3 → 1 frisch, 5 einfrieren</t>
+          <t>Charge 1/7 → 1 frisch, 2 einfrieren</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1132,31 @@
       <c r="A15" s="14" t="inlineStr"/>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Beeren Tartelette</t>
+          <t>Donauwelle</t>
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>60 Stueck → 8 frisch, 52 einfrieren</t>
+          <t>Charge 2/3 → 1 frisch, 5 einfrieren</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>DONNERSTAG</t>
+      <c r="A16" s="14" t="inlineStr"/>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Kaese-Rhabarber Schnitte</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Charge 1/3 — Pflicht (Donnerstag=mind. 1/Tag) → 1 frisch, 5 einfrieren</t>
         </is>
       </c>
     </row>
@@ -1161,31 +1164,22 @@
       <c r="A17" s="14" t="inlineStr"/>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Kaesekuchen</t>
+          <t>Kaese-Rhabarber Schnitte</t>
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Charge 3/10</t>
+          <t>Charge 3/3 → 1 frisch, 5 einfrieren</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="14" t="inlineStr"/>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>Kaesekuchen</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>Charge 4/10</t>
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>FREITAG</t>
         </is>
       </c>
     </row>
@@ -1193,15 +1187,15 @@
       <c r="A19" s="14" t="inlineStr"/>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Bienenstich</t>
+          <t>Kaesekuchen</t>
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Charge 2/3 → 1 frisch, 5 einfrieren</t>
+          <t>Charge 1/10</t>
         </is>
       </c>
     </row>
@@ -1209,15 +1203,15 @@
       <c r="A20" s="14" t="inlineStr"/>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Lauch-Speck Quiche</t>
+          <t>Kaesekuchen</t>
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Charge 1/7 → 1 frisch, 2 einfrieren</t>
+          <t>Charge 2/10</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1219,7 @@
       <c r="A21" s="14" t="inlineStr"/>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Donauwelle</t>
+          <t>Bienenstich</t>
         </is>
       </c>
       <c r="C21" s="14" t="n">
@@ -1233,7 +1227,7 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Charge 2/3 → 1 frisch, 5 einfrieren</t>
+          <t>Charge 1/3 → 2 frisch, 4 einfrieren</t>
         </is>
       </c>
     </row>
@@ -1241,22 +1235,31 @@
       <c r="A22" s="14" t="inlineStr"/>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Kaese-Rhabarber Schnitte</t>
+          <t>Lauch-Speck Quiche</t>
         </is>
       </c>
       <c r="C22" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Charge 2/7 → 2 frisch, 1 einfrieren</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="14" t="inlineStr"/>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Donauwelle</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>Charge 1/3 — Pflicht (Donnerstag=mind. 1/Tag) → 1 frisch, 5 einfrieren</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>FREITAG</t>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Charge 1/3 → 2 frisch, 4 einfrieren</t>
         </is>
       </c>
     </row>
@@ -1264,105 +1267,24 @@
       <c r="A24" s="14" t="inlineStr"/>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Kaesekuchen</t>
+          <t>Kaese-Rhabarber Schnitte</t>
         </is>
       </c>
       <c r="C24" s="14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Charge 1/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="14" t="inlineStr"/>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>Kaesekuchen</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Charge 2/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="14" t="inlineStr"/>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>Bienenstich</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>Charge 1/3 → 2 frisch, 4 einfrieren</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="14" t="inlineStr"/>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>Lauch-Speck Quiche</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Charge 2/7 → 2 frisch, 1 einfrieren</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="14" t="inlineStr"/>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>Donauwelle</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Charge 1/3 → 2 frisch, 4 einfrieren</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="14" t="inlineStr"/>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>Kaese-Rhabarber Schnitte</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>Charge 3/3 → 2 frisch, 4 einfrieren</t>
+          <t>Charge 2/3 → 2 frisch, 4 einfrieren</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
